--- a/韦广波爬虫自查结果.xlsx
+++ b/韦广波爬虫自查结果.xlsx
@@ -20185,7 +20185,7 @@
         <v>916</v>
       </c>
       <c r="G476" s="16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H476" s="16" t="s">
         <v>17</v>
@@ -21241,7 +21241,7 @@
         <v>998</v>
       </c>
       <c r="G509" s="16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H509" s="16" t="s">
         <v>17</v>
@@ -21305,7 +21305,7 @@
         <v>1001</v>
       </c>
       <c r="G511" s="16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H511" s="16" t="s">
         <v>17</v>
@@ -21724,7 +21724,7 @@
         <v>1024</v>
       </c>
       <c r="G524" s="16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H524" s="16" t="s">
         <v>1025</v>
@@ -22684,7 +22684,7 @@
         <v>1080</v>
       </c>
       <c r="G554" s="16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H554" s="16" t="s">
         <v>17</v>
@@ -24796,7 +24796,7 @@
         <v>1188</v>
       </c>
       <c r="G620" s="16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H620" s="16" t="s">
         <v>17</v>
